--- a/工作数据.xlsx
+++ b/工作数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18525" windowHeight="17670"/>
+    <workbookView windowWidth="22635" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Method</t>
   </si>
@@ -32,6 +32,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>SGRL(</t>
     </r>
     <r>
@@ -82,6 +89,75 @@
   <si>
     <t xml:space="preserve">95.847 ± 0.0003 </t>
   </si>
+  <si>
+    <t>homo-dot-0.3</t>
+  </si>
+  <si>
+    <t>87.664 ± 0.0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.42 ± 0.0003 </t>
+  </si>
+  <si>
+    <t>94.113 ± 0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.269 ± 0.0003 </t>
+  </si>
+  <si>
+    <t>detach-dot-0.3</t>
+  </si>
+  <si>
+    <t>87.48 ± 0.0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.91 ± 0.0003 </t>
+  </si>
+  <si>
+    <t>94.13 ± 0.00001</t>
+  </si>
+  <si>
+    <t>detach-dot-0.7</t>
+  </si>
+  <si>
+    <t>93.84 ± 0.00003</t>
+  </si>
+  <si>
+    <t>94.25 ± 0.0001</t>
+  </si>
+  <si>
+    <t>homo-cos-0.3</t>
+  </si>
+  <si>
+    <t>93.78 ± 0.000000</t>
+  </si>
+  <si>
+    <t>图数据审计</t>
+  </si>
+  <si>
+    <t>点</t>
+  </si>
+  <si>
+    <t>特征维度</t>
+  </si>
+  <si>
+    <t>边</t>
+  </si>
+  <si>
+    <t>粒球审计</t>
+  </si>
+  <si>
+    <t>总数量</t>
+  </si>
+  <si>
+    <t>最大球</t>
+  </si>
+  <si>
+    <t>平均球</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -93,7 +169,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +199,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="NimbusRomNo9L-Medi"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -274,7 +364,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,6 +391,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -486,7 +588,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -498,17 +600,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -530,6 +621,28 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -641,10 +754,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -653,137 +766,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -793,29 +906,62 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1136,132 +1282,267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.8833333333333" customWidth="1"/>
     <col min="2" max="3" width="16.2416666666667" customWidth="1"/>
     <col min="4" max="4" width="14.9" customWidth="1"/>
     <col min="5" max="5" width="14.5083333333333" customWidth="1"/>
     <col min="6" max="6" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="16.5333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="26" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="A9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="14">
+        <v>13752</v>
+      </c>
+      <c r="D9" s="14">
+        <v>7650</v>
+      </c>
+      <c r="E9" s="14">
+        <v>18333</v>
+      </c>
+      <c r="F9" s="14">
+        <v>34493</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="14">
+        <v>767</v>
+      </c>
+      <c r="D10" s="14">
+        <v>745</v>
+      </c>
+      <c r="E10" s="14">
+        <v>6805</v>
+      </c>
+      <c r="F10" s="14">
+        <v>8415</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="17"/>
+      <c r="B11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="14">
+        <v>491722</v>
+      </c>
+      <c r="D11" s="14">
+        <v>238162</v>
+      </c>
+      <c r="E11" s="14">
+        <v>163788</v>
+      </c>
+      <c r="F11" s="14">
+        <v>495924</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="19">
+        <v>465</v>
+      </c>
+      <c r="D12" s="19">
+        <v>240</v>
+      </c>
+      <c r="E12" s="19">
+        <v>265</v>
+      </c>
+      <c r="F12" s="19">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="20"/>
+      <c r="B13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="19">
+        <v>5897</v>
+      </c>
+      <c r="D13" s="19">
+        <v>2470</v>
+      </c>
+      <c r="E13" s="19">
+        <v>806</v>
+      </c>
+      <c r="F13" s="19">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="21"/>
+      <c r="B14" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="19">
+        <v>30</v>
+      </c>
+      <c r="D14" s="19">
+        <v>32</v>
+      </c>
+      <c r="E14" s="19">
+        <v>78</v>
+      </c>
+      <c r="F14" s="19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
